--- a/books.xlsx
+++ b/books.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Raw" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Clean" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +438,11 @@
           <t>link</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -444,8 +450,10 @@
           <t>A Light in the Attic</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>51.77</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>51.77</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -456,6 +464,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/a-light-in-the-attic_1000/index.html</t>
         </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -464,8 +475,10 @@
           <t>Tipping the Velvet</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>53.74</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>53.74</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -476,6 +489,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/tipping-the-velvet_999/index.html</t>
         </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -484,8 +500,10 @@
           <t>Soumission</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>50.1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>50.10</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -496,6 +514,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/soumission_998/index.html</t>
         </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -504,8 +525,10 @@
           <t>Sharp Objects</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>47.82</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>47.82</t>
+        </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -516,6 +539,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/sharp-objects_997/index.html</t>
         </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -524,8 +550,10 @@
           <t>Sapiens: A Brief History of Humankind</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>54.23</v>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>54.23</t>
+        </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -536,6 +564,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/sapiens-a-brief-history-of-humankind_996/index.html</t>
         </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -544,8 +575,10 @@
           <t>The Requiem Red</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>22.65</v>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>22.65</t>
+        </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -556,6 +589,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/the-requiem-red_995/index.html</t>
         </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -564,8 +600,10 @@
           <t>The Dirty Little Secrets of Getting Your Dream Job</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>33.34</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>33.34</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,6 +614,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/the-dirty-little-secrets-of-getting-your-dream-job_994/index.html</t>
         </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -584,8 +625,10 @@
           <t>The Coming Woman: A Novel Based on the Life of the Infamous Feminist, Victoria Woodhull</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>17.93</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>17.93</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -596,6 +639,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/the-coming-woman-a-novel-based-on-the-life-of-the-infamous-feminist-victoria-woodhull_993/index.html</t>
         </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -604,8 +650,10 @@
           <t>The Boys in the Boat: Nine Americans and Their Epic Quest for Gold at the 1936 Berlin Olympics</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>22.6</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.60</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -616,6 +664,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/the-boys-in-the-boat-nine-americans-and-their-epic-quest-for-gold-at-the-1936-berlin-olympics_992/index.html</t>
         </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -624,8 +675,10 @@
           <t>The Black Maria</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>52.15</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>52.15</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -636,6 +689,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/the-black-maria_991/index.html</t>
         </is>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -644,8 +700,10 @@
           <t>Starving Hearts (Triangular Trade Trilogy, #1)</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>13.99</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>13.99</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -656,6 +714,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/starving-hearts-triangular-trade-trilogy-1_990/index.html</t>
         </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -664,8 +725,10 @@
           <t>Shakespeare's Sonnets</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>20.66</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20.66</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -676,6 +739,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/shakespeares-sonnets_989/index.html</t>
         </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -684,8 +750,10 @@
           <t>Set Me Free</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>17.46</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>17.46</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -696,6 +764,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/set-me-free_988/index.html</t>
         </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -704,8 +775,10 @@
           <t>Scott Pilgrim's Precious Little Life (Scott Pilgrim #1)</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>52.29</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>52.29</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -716,6 +789,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/scott-pilgrims-precious-little-life-scott-pilgrim-1_987/index.html</t>
         </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -724,8 +800,10 @@
           <t>Rip it Up and Start Again</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>35.02</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>35.02</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -736,6 +814,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/rip-it-up-and-start-again_986/index.html</t>
         </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -744,8 +825,10 @@
           <t>Our Band Could Be Your Life: Scenes from the American Indie Underground, 1981-1991</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>57.25</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>57.25</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -756,6 +839,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/our-band-could-be-your-life-scenes-from-the-american-indie-underground-1981-1991_985/index.html</t>
         </is>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -764,8 +850,10 @@
           <t>Olio</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>23.88</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>23.88</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -776,6 +864,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/olio_984/index.html</t>
         </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -784,8 +875,10 @@
           <t>Mesaerion: The Best Science Fiction Stories 1800-1849</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>37.59</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>37.59</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -796,6 +889,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/mesaerion-the-best-science-fiction-stories-1800-1849_983/index.html</t>
         </is>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -804,8 +900,10 @@
           <t>Libertarianism for Beginners</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>51.33</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>51.33</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -816,6 +914,9 @@
         <is>
           <t>https://books.toscrape.com/catalogue/libertarianism-for-beginners_982/index.html</t>
         </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -824,18 +925,4164 @@
           <t>It's Only the Himalayas</t>
         </is>
       </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>45.17</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/its-only-the-himalayas_981/index.html</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>In Her Wake</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>12.84</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-her-wake_980/index.html</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>How Music Works</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>37.32</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/how-music-works_979/index.html</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Foolproof Preserving: A Guide to Small Batch Jams, Jellies, Pickles, Condiments, and More: A Foolproof Guide to Making Small Batch Jams, Jellies, Pickles, Condiments, and More</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>30.52</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chase Me (Paris Nights #2)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>25.27</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/chase-me-paris-nights-2_977/index.html</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Black Dust</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>34.53</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/black-dust_976/index.html</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Birdsong: A Story in Pictures</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>54.64</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/birdsong-a-story-in-pictures_975/index.html</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>America's Cradle of Quarterbacks: Western Pennsylvania's Football Factory from Johnny Unitas to Joe Montana</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>22.50</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/americas-cradle-of-quarterbacks-western-pennsylvanias-football-factory-from-johnny-unitas-to-joe-montana_974/index.html</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Aladdin and His Wonderful Lamp</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>53.13</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/aladdin-and-his-wonderful-lamp_973/index.html</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Worlds Elsewhere: Journeys Around Shakespeareâs Globe</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>40.30</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Wall and Piece</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/wall-and-piece_971/index.html</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>17.66</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-four-agreements-a-practical-guide-to-personal-freedom_970/index.html</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The Five Love Languages: How to Express Heartfelt Commitment to Your Mate</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>31.05</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-five-love-languages-how-to-express-heartfelt-commitment-to-your-mate_969/index.html</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>The Elephant Tree</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>23.82</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-elephant-tree_968/index.html</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>The Bear and the Piano</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>36.89</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-bear-and-the-piano_967/index.html</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Sophie's World</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>15.94</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/sophies-world_966/index.html</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Penny Maybe</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>33.29</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/penny-maybe_965/index.html</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Maude (1883-1993):She Grew Up with the country</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>18.02</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/maude-1883-1993she-grew-up-with-the-country_964/index.html</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>In a Dark, Dark Wood</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19.63</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-a-dark-dark-wood_963/index.html</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Behind Closed Doors</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>52.22</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/behind-closed-doors_962/index.html</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>You can't bury them all: Poems</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>33.63</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/you-cant-bury-them-all-poems_961/index.html</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Slow States of Collapse: Poems</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>57.31</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/slow-states-of-collapse-poems_960/index.html</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Reasons to Stay Alive</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>26.41</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/reasons-to-stay-alive_959/index.html</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Private Paris (Private #10)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>47.61</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/private-paris-private-10_958/index.html</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>#HigherSelfie: Wake Up Your Life. Free Your Soul. Find Your Tribe.</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>23.11</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/higherselfie-wake-up-your-life-free-your-soul-find-your-tribe_957/index.html</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Without Borders (Wanderlove #1)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>45.07</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/without-borders-wanderlove-1_956/index.html</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>When We Collided</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>31.77</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/when-we-collided_955/index.html</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>We Love You, Charlie Freeman</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>50.27</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/we-love-you-charlie-freeman_954/index.html</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Untitled Collection: Sabbath Poems 2014</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>14.27</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/untitled-collection-sabbath-poems-2014_953/index.html</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unseen City: The Majesty of Pigeons, the Discreet Charm of Snails &amp; Other Wonders of the Urban Wilderness</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>44.18</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/unseen-city-the-majesty-of-pigeons-the-discreet-charm-of-snails-other-wonders-of-the-urban-wilderness_952/index.html</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Unicorn Tracks</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>18.78</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/unicorn-tracks_951/index.html</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unbound: How Eight Technologies Made Us Human, Transformed Society, and Brought Our World to the Brink</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>25.52</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/unbound-how-eight-technologies-made-us-human-transformed-society-and-brought-our-world-to-the-brink_950/index.html</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Tsubasa: WoRLD CHRoNiCLE 2 (Tsubasa WoRLD CHRoNiCLE #2)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>16.28</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/tsubasa-world-chronicle-2-tsubasa-world-chronicle-2_949/index.html</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Throwing Rocks at the Google Bus: How Growth Became the Enemy of Prosperity</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>31.12</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/throwing-rocks-at-the-google-bus-how-growth-became-the-enemy-of-prosperity_948/index.html</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>This One Summer</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>19.49</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/this-one-summer_947/index.html</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Thirst</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>17.27</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/thirst_946/index.html</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>The Torch Is Passed: A Harding Family Story</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>19.09</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-torch-is-passed-a-harding-family-story_945/index.html</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>The Secret of Dreadwillow Carse</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>56.13</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-secret-of-dreadwillow-carse_944/index.html</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>The Pioneer Woman Cooks: Dinnertime: Comfort Classics, Freezer Food, 16-Minute Meals, and Other Delicious Ways to Solve Supper!</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>56.41</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-pioneer-woman-cooks-dinnertime-comfort-classics-freezer-food-16-minute-meals-and-other-delicious-ways-to-solve-supper_943/index.html</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>The Past Never Ends</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>56.50</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-past-never-ends_942/index.html</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>The Natural History of Us (The Fine Art of Pretending #2)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>45.22</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-natural-history-of-us-the-fine-art-of-pretending-2_941/index.html</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>The Nameless City (The Nameless City #1)</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>38.16</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-nameless-city-the-nameless-city-1_940/index.html</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>The Murder That Never Was (Forensic Instincts #5)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>54.11</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-murder-that-never-was-forensic-instincts-5_939/index.html</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>The Most Perfect Thing: Inside (and Outside) a Bird's Egg</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>42.96</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-most-perfect-thing-inside-and-outside-a-birds-egg_938/index.html</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>The Mindfulness and Acceptance Workbook for Anxiety: A Guide to Breaking Free from Anxiety, Phobias, and Worry Using Acceptance and Commitment Therapy</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>23.89</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-mindfulness-and-acceptance-workbook-for-anxiety-a-guide-to-breaking-free-from-anxiety-phobias-and-worry-using-acceptance-and-commitment-therapy_937/index.html</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>The Life-Changing Magic of Tidying Up: The Japanese Art of Decluttering and Organizing</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>16.77</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-life-changing-magic-of-tidying-up-the-japanese-art-of-decluttering-and-organizing_936/index.html</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>The Inefficiency Assassin: Time Management Tactics for Working Smarter, Not Longer</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>20.59</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-inefficiency-assassin-time-management-tactics-for-working-smarter-not-longer_935/index.html</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>The Gutsy Girl: Escapades for Your Life of Epic Adventure</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>37.13</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-gutsy-girl-escapades-for-your-life-of-epic-adventure_934/index.html</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>The Electric Pencil: Drawings from Inside State Hospital No. 3</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>56.06</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-electric-pencil-drawings-from-inside-state-hospital-no-3_933/index.html</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>The Death of Humanity: and the Case for Life</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>58.11</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-death-of-humanity-and-the-case-for-life_932/index.html</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>The Bulletproof Diet: Lose up to a Pound a Day, Reclaim Energy and Focus, Upgrade Your Life</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>49.05</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-bulletproof-diet-lose-up-to-a-pound-a-day-reclaim-energy-and-focus-upgrade-your-life_931/index.html</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>The Art Forger</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>40.76</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-art-forger_930/index.html</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>The Age of Genius: The Seventeenth Century and the Birth of the Modern Mind</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>19.73</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-age-of-genius-the-seventeenth-century-and-the-birth-of-the-modern-mind_929/index.html</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>The Activist's Tao Te Ching: Ancient Advice for a Modern Revolution</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>32.24</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-activists-tao-te-ching-ancient-advice-for-a-modern-revolution_928/index.html</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Spark Joy: An Illustrated Master Class on the Art of Organizing and Tidying Up</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>41.83</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/spark-joy-an-illustrated-master-class-on-the-art-of-organizing-and-tidying-up_927/index.html</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Soul Reader</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>39.58</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/soul-reader_926/index.html</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>39.25</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/security_925/index.html</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Saga, Volume 6 (Saga (Collected Editions) #6)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>25.02</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/saga-volume-6-saga-collected-editions-6_924/index.html</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Saga, Volume 5 (Saga (Collected Editions) #5)</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>51.04</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/saga-volume-5-saga-collected-editions-5_923/index.html</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Reskilling America: Learning to Labor in the Twenty-First Century</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>19.83</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/reskilling-america-learning-to-labor-in-the-twenty-first-century_922/index.html</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Rat Queens, Vol. 3: Demons (Rat Queens (Collected Editions) #11-15)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>50.40</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/rat-queens-vol-3-demons-rat-queens-collected-editions-11-15_921/index.html</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Princess Jellyfish 2-in-1 Omnibus, Vol. 01 (Princess Jellyfish 2-in-1 Omnibus #1)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>13.61</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/princess-jellyfish-2-in-1-omnibus-vol-01-princess-jellyfish-2-in-1-omnibus-1_920/index.html</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Princess Between Worlds (Wide-Awake Princess #5)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>13.34</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/princess-between-worlds-wide-awake-princess-5_919/index.html</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Pop Gun War, Volume 1: Gift</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>18.97</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/pop-gun-war-volume-1-gift_918/index.html</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Political Suicide: Missteps, Peccadilloes, Bad Calls, Backroom Hijinx, Sordid Pasts, Rotten Breaks, and Just Plain Dumb Mistakes in the Annals of American Politics</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>36.28</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/political-suicide-missteps-peccadilloes-bad-calls-backroom-hijinx-sordid-pasts-rotten-breaks-and-just-plain-dumb-mistakes-in-the-annals-of-american-politics_917/index.html</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Patience</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>10.16</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/patience_916/index.html</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Outcast, Vol. 1: A Darkness Surrounds Him (Outcast #1)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>15.44</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/outcast-vol-1-a-darkness-surrounds-him-outcast-1_915/index.html</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>orange: The Complete Collection 1 (orange: The Complete Collection #1)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>48.41</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/orange-the-complete-collection-1-orange-the-complete-collection-1_914/index.html</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Online Marketing for Busy Authors: A Step-By-Step Guide</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>46.35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/online-marketing-for-busy-authors-a-step-by-step-guide_913/index.html</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>On a Midnight Clear</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>14.07</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/on-a-midnight-clear_912/index.html</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Obsidian (Lux #1)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>14.86</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/obsidian-lux-1_911/index.html</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>My Paris Kitchen: Recipes and Stories</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>33.37</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/my-paris-kitchen-recipes-and-stories_910/index.html</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Masks and Shadows</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>56.40</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/masks-and-shadows_909/index.html</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Mama Tried: Traditional Italian Cooking for the Screwed, Crude, Vegan, and Tattooed</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>14.02</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/mama-tried-traditional-italian-cooking-for-the-screwed-crude-vegan-and-tattooed_908/index.html</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Lumberjanes, Vol. 2: Friendship to the Max (Lumberjanes #5-8)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>46.91</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-2-friendship-to-the-max-lumberjanes-5-8_907/index.html</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Lumberjanes, Vol. 1: Beware the Kitten Holy (Lumberjanes #1-4)</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>45.61</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Three</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-1-beware-the-kitten-holy-lumberjanes-1-4_906/index.html</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Lumberjanes Vol. 3: A Terrible Plan (Lumberjanes #9-12)</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>19.92</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-3-a-terrible-plan-lumberjanes-9-12_905/index.html</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Layered: Baking, Building, and Styling Spectacular Cakes</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>40.11</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>One</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/layered-baking-building-and-styling-spectacular-cakes_904/index.html</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Judo: Seven Steps to Black Belt (an Introductory Guide for Beginners)</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>53.90</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Two</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/judo-seven-steps-to-black-belt-an-introductory-guide-for-beginners_903/index.html</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>35.67</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Five</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/join_902/index.html</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>In the Country We Love: My Family Divided</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>22.00</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Four</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-the-country-we-love-my-family-divided_901/index.html</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E101"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>rating</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>link</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>page</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Patience</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/patience_916/index.html</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>In Her Wake</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-her-wake_980/index.html</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Princess Between Worlds (Wide-Awake Princess #5)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="C4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/princess-between-worlds-wide-awake-princess-5_919/index.html</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Princess Jellyfish 2-in-1 Omnibus, Vol. 01 (Princess Jellyfish 2-in-1 Omnibus #1)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>13.61</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/princess-jellyfish-2-in-1-omnibus-vol-01-princess-jellyfish-2-in-1-omnibus-1_920/index.html</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Starving Hearts (Triangular Trade Trilogy, #1)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>13.99</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/starving-hearts-triangular-trade-trilogy-1_990/index.html</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mama Tried: Traditional Italian Cooking for the Screwed, Crude, Vegan, and Tattooed</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/mama-tried-traditional-italian-cooking-for-the-screwed-crude-vegan-and-tattooed_908/index.html</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>On a Midnight Clear</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/on-a-midnight-clear_912/index.html</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Untitled Collection: Sabbath Poems 2014</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14.27</v>
+      </c>
+      <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/untitled-collection-sabbath-poems-2014_953/index.html</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Obsidian (Lux #1)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/obsidian-lux-1_911/index.html</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Outcast, Vol. 1: A Darkness Surrounds Him (Outcast #1)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/outcast-vol-1-a-darkness-surrounds-him-outcast-1_915/index.html</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Sophie's World</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>15.94</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/sophies-world_966/index.html</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Tsubasa: WoRLD CHRoNiCLE 2 (Tsubasa WoRLD CHRoNiCLE #2)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>16.28</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/tsubasa-world-chronicle-2-tsubasa-world-chronicle-2_949/index.html</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>The Life-Changing Magic of Tidying Up: The Japanese Art of Decluttering and Organizing</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>16.77</v>
+      </c>
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-life-changing-magic-of-tidying-up-the-japanese-art-of-decluttering-and-organizing_936/index.html</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Thirst</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/thirst_946/index.html</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Set Me Free</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>17.46</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/set-me-free_988/index.html</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>The Four Agreements: A Practical Guide to Personal Freedom</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-four-agreements-a-practical-guide-to-personal-freedom_970/index.html</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>The Coming Woman: A Novel Based on the Life of the Infamous Feminist, Victoria Woodhull</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-coming-woman-a-novel-based-on-the-life-of-the-infamous-feminist-victoria-woodhull_993/index.html</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Maude (1883-1993):She Grew Up with the country</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/maude-1883-1993she-grew-up-with-the-country_964/index.html</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Unicorn Tracks</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>18.78</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/unicorn-tracks_951/index.html</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Pop Gun War, Volume 1: Gift</t>
+        </is>
+      </c>
       <c r="B21" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/pop-gun-war-volume-1-gift_918/index.html</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>The Torch Is Passed: A Harding Family Story</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-torch-is-passed-a-harding-family-story_945/index.html</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>This One Summer</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/this-one-summer_947/index.html</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>In a Dark, Dark Wood</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-a-dark-dark-wood_963/index.html</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>The Age of Genius: The Seventeenth Century and the Birth of the Modern Mind</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>19.73</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-age-of-genius-the-seventeenth-century-and-the-birth-of-the-modern-mind_929/index.html</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Reskilling America: Learning to Labor in the Twenty-First Century</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>19.83</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/reskilling-america-learning-to-labor-in-the-twenty-first-century_922/index.html</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Lumberjanes Vol. 3: A Terrible Plan (Lumberjanes #9-12)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>19.92</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-3-a-terrible-plan-lumberjanes-9-12_905/index.html</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>The Inefficiency Assassin: Time Management Tactics for Working Smarter, Not Longer</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-inefficiency-assassin-time-management-tactics-for-working-smarter-not-longer_935/index.html</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Shakespeare's Sonnets</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>20.66</v>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/shakespeares-sonnets_989/index.html</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>In the Country We Love: My Family Divided</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>22</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/in-the-country-we-love-my-family-divided_901/index.html</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>America's Cradle of Quarterbacks: Western Pennsylvania's Football Factory from Johnny Unitas to Joe Montana</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/americas-cradle-of-quarterbacks-western-pennsylvanias-football-factory-from-johnny-unitas-to-joe-montana_974/index.html</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>The Boys in the Boat: Nine Americans and Their Epic Quest for Gold at the 1936 Berlin Olympics</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-boys-in-the-boat-nine-americans-and-their-epic-quest-for-gold-at-the-1936-berlin-olympics_992/index.html</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>The Requiem Red</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-requiem-red_995/index.html</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>#HigherSelfie: Wake Up Your Life. Free Your Soul. Find Your Tribe.</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="C34" t="n">
+        <v>5</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/higherselfie-wake-up-your-life-free-your-soul-find-your-tribe_957/index.html</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>The Elephant Tree</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>23.82</v>
+      </c>
+      <c r="C35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-elephant-tree_968/index.html</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Olio</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/olio_984/index.html</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>The Mindfulness and Acceptance Workbook for Anxiety: A Guide to Breaking Free from Anxiety, Phobias, and Worry Using Acceptance and Commitment Therapy</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="C37" t="n">
+        <v>4</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-mindfulness-and-acceptance-workbook-for-anxiety-a-guide-to-breaking-free-from-anxiety-phobias-and-worry-using-acceptance-and-commitment-therapy_937/index.html</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Saga, Volume 6 (Saga (Collected Editions) #6)</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="C38" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/saga-volume-6-saga-collected-editions-6_924/index.html</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chase Me (Paris Nights #2)</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="C39" t="n">
+        <v>5</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/chase-me-paris-nights-2_977/index.html</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Unbound: How Eight Technologies Made Us Human, Transformed Society, and Brought Our World to the Brink</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>25.52</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/unbound-how-eight-technologies-made-us-human-transformed-society-and-brought-our-world-to-the-brink_950/index.html</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Reasons to Stay Alive</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>26.41</v>
+      </c>
+      <c r="C41" t="n">
+        <v>2</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/reasons-to-stay-alive_959/index.html</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Foolproof Preserving: A Guide to Small Batch Jams, Jellies, Pickles, Condiments, and More: A Foolproof Guide to Making Small Batch Jams, Jellies, Pickles, Condiments, and More</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>30.52</v>
+      </c>
+      <c r="C42" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/foolproof-preserving-a-guide-to-small-batch-jams-jellies-pickles-condiments-and-more-a-foolproof-guide-to-making-small-batch-jams-jellies-pickles-condiments-and-more_978/index.html</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>The Five Love Languages: How to Express Heartfelt Commitment to Your Mate</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-five-love-languages-how-to-express-heartfelt-commitment-to-your-mate_969/index.html</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Throwing Rocks at the Google Bus: How Growth Became the Enemy of Prosperity</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>31.12</v>
+      </c>
+      <c r="C44" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/throwing-rocks-at-the-google-bus-how-growth-became-the-enemy-of-prosperity_948/index.html</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>When We Collided</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/when-we-collided_955/index.html</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>The Activist's Tao Te Ching: Ancient Advice for a Modern Revolution</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>32.24</v>
+      </c>
+      <c r="C46" t="n">
+        <v>5</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-activists-tao-te-ching-ancient-advice-for-a-modern-revolution_928/index.html</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Penny Maybe</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>33.29</v>
+      </c>
+      <c r="C47" t="n">
+        <v>3</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/penny-maybe_965/index.html</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>The Dirty Little Secrets of Getting Your Dream Job</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="C48" t="n">
+        <v>4</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-dirty-little-secrets-of-getting-your-dream-job_994/index.html</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>My Paris Kitchen: Recipes and Stories</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>33.37</v>
+      </c>
+      <c r="C49" t="n">
+        <v>2</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/my-paris-kitchen-recipes-and-stories_910/index.html</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>You can't bury them all: Poems</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="C50" t="n">
+        <v>2</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/you-cant-bury-them-all-poems_961/index.html</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Black Dust</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="C51" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/black-dust_976/index.html</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Rip it Up and Start Again</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="C52" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/rip-it-up-and-start-again_986/index.html</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>35.67</v>
+      </c>
+      <c r="C53" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/join_902/index.html</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Political Suicide: Missteps, Peccadilloes, Bad Calls, Backroom Hijinx, Sordid Pasts, Rotten Breaks, and Just Plain Dumb Mistakes in the Annals of American Politics</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>36.28</v>
+      </c>
+      <c r="C54" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/political-suicide-missteps-peccadilloes-bad-calls-backroom-hijinx-sordid-pasts-rotten-breaks-and-just-plain-dumb-mistakes-in-the-annals-of-american-politics_917/index.html</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>The Bear and the Piano</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>36.89</v>
+      </c>
+      <c r="C55" t="n">
+        <v>1</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-bear-and-the-piano_967/index.html</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>The Gutsy Girl: Escapades for Your Life of Epic Adventure</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>37.13</v>
+      </c>
+      <c r="C56" t="n">
+        <v>1</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-gutsy-girl-escapades-for-your-life-of-epic-adventure_934/index.html</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>How Music Works</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>37.32</v>
+      </c>
+      <c r="C57" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/how-music-works_979/index.html</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Mesaerion: The Best Science Fiction Stories 1800-1849</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>37.59</v>
+      </c>
+      <c r="C58" t="n">
+        <v>1</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/mesaerion-the-best-science-fiction-stories-1800-1849_983/index.html</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>The Nameless City (The Nameless City #1)</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>38.16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-nameless-city-the-nameless-city-1_940/index.html</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>39.25</v>
+      </c>
+      <c r="C60" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/security_925/index.html</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Soul Reader</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>39.58</v>
+      </c>
+      <c r="C61" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/soul-reader_926/index.html</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Layered: Baking, Building, and Styling Spectacular Cakes</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>40.11</v>
+      </c>
+      <c r="C62" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/layered-baking-building-and-styling-spectacular-cakes_904/index.html</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Worlds Elsewhere: Journeys Around Shakespeareâs Globe</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="C63" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/worlds-elsewhere-journeys-around-shakespeares-globe_972/index.html</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>The Art Forger</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>40.76</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-art-forger_930/index.html</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Spark Joy: An Illustrated Master Class on the Art of Organizing and Tidying Up</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>41.83</v>
+      </c>
+      <c r="C65" t="n">
+        <v>4</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/spark-joy-an-illustrated-master-class-on-the-art-of-organizing-and-tidying-up_927/index.html</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>The Most Perfect Thing: Inside (and Outside) a Bird's Egg</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>42.96</v>
+      </c>
+      <c r="C66" t="n">
+        <v>4</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-most-perfect-thing-inside-and-outside-a-birds-egg_938/index.html</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Wall and Piece</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="C67" t="n">
+        <v>4</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/wall-and-piece_971/index.html</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unseen City: The Majesty of Pigeons, the Discreet Charm of Snails &amp; Other Wonders of the Urban Wilderness</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>44.18</v>
+      </c>
+      <c r="C68" t="n">
+        <v>4</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/unseen-city-the-majesty-of-pigeons-the-discreet-charm-of-snails-other-wonders-of-the-urban-wilderness_952/index.html</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Without Borders (Wanderlove #1)</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>45.07</v>
+      </c>
+      <c r="C69" t="n">
+        <v>2</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/without-borders-wanderlove-1_956/index.html</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>It's Only the Himalayas</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
         <v>45.17</v>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Two</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C70" t="n">
+        <v>2</v>
+      </c>
+      <c r="D70" t="inlineStr">
         <is>
           <t>https://books.toscrape.com/catalogue/its-only-the-himalayas_981/index.html</t>
         </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>The Natural History of Us (The Fine Art of Pretending #2)</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>45.22</v>
+      </c>
+      <c r="C71" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-natural-history-of-us-the-fine-art-of-pretending-2_941/index.html</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Lumberjanes, Vol. 1: Beware the Kitten Holy (Lumberjanes #1-4)</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>45.61</v>
+      </c>
+      <c r="C72" t="n">
+        <v>3</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-1-beware-the-kitten-holy-lumberjanes-1-4_906/index.html</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Online Marketing for Busy Authors: A Step-By-Step Guide</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="C73" t="n">
+        <v>1</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/online-marketing-for-busy-authors-a-step-by-step-guide_913/index.html</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Lumberjanes, Vol. 2: Friendship to the Max (Lumberjanes #5-8)</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>46.91</v>
+      </c>
+      <c r="C74" t="n">
+        <v>2</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/lumberjanes-vol-2-friendship-to-the-max-lumberjanes-5-8_907/index.html</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Private Paris (Private #10)</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>47.61</v>
+      </c>
+      <c r="C75" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/private-paris-private-10_958/index.html</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Sharp Objects</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>47.82</v>
+      </c>
+      <c r="C76" t="n">
+        <v>4</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/sharp-objects_997/index.html</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>orange: The Complete Collection 1 (orange: The Complete Collection #1)</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>48.41</v>
+      </c>
+      <c r="C77" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/orange-the-complete-collection-1-orange-the-complete-collection-1_914/index.html</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>The Bulletproof Diet: Lose up to a Pound a Day, Reclaim Energy and Focus, Upgrade Your Life</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>49.05</v>
+      </c>
+      <c r="C78" t="n">
+        <v>3</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-bulletproof-diet-lose-up-to-a-pound-a-day-reclaim-energy-and-focus-upgrade-your-life_931/index.html</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Soumission</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="C79" t="n">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/soumission_998/index.html</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>We Love You, Charlie Freeman</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>50.27</v>
+      </c>
+      <c r="C80" t="n">
+        <v>5</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/we-love-you-charlie-freeman_954/index.html</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Rat Queens, Vol. 3: Demons (Rat Queens (Collected Editions) #11-15)</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="C81" t="n">
+        <v>3</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/rat-queens-vol-3-demons-rat-queens-collected-editions-11-15_921/index.html</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Saga, Volume 5 (Saga (Collected Editions) #5)</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>51.04</v>
+      </c>
+      <c r="C82" t="n">
+        <v>2</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/saga-volume-5-saga-collected-editions-5_923/index.html</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Libertarianism for Beginners</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="C83" t="n">
+        <v>2</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/libertarianism-for-beginners_982/index.html</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>A Light in the Attic</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>51.77</v>
+      </c>
+      <c r="C84" t="n">
+        <v>3</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/a-light-in-the-attic_1000/index.html</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>The Black Maria</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>52.15</v>
+      </c>
+      <c r="C85" t="n">
+        <v>1</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-black-maria_991/index.html</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Behind Closed Doors</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>52.22</v>
+      </c>
+      <c r="C86" t="n">
+        <v>4</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/behind-closed-doors_962/index.html</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Scott Pilgrim's Precious Little Life (Scott Pilgrim #1)</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>52.29</v>
+      </c>
+      <c r="C87" t="n">
+        <v>5</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/scott-pilgrims-precious-little-life-scott-pilgrim-1_987/index.html</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Aladdin and His Wonderful Lamp</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>53.13</v>
+      </c>
+      <c r="C88" t="n">
+        <v>3</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/aladdin-and-his-wonderful-lamp_973/index.html</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Tipping the Velvet</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>53.74</v>
+      </c>
+      <c r="C89" t="n">
+        <v>1</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/tipping-the-velvet_999/index.html</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Judo: Seven Steps to Black Belt (an Introductory Guide for Beginners)</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="C90" t="n">
+        <v>2</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/judo-seven-steps-to-black-belt-an-introductory-guide-for-beginners_903/index.html</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>The Murder That Never Was (Forensic Instincts #5)</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>54.11</v>
+      </c>
+      <c r="C91" t="n">
+        <v>3</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-murder-that-never-was-forensic-instincts-5_939/index.html</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Sapiens: A Brief History of Humankind</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>54.23</v>
+      </c>
+      <c r="C92" t="n">
+        <v>5</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/sapiens-a-brief-history-of-humankind_996/index.html</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Birdsong: A Story in Pictures</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>54.64</v>
+      </c>
+      <c r="C93" t="n">
+        <v>3</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/birdsong-a-story-in-pictures_975/index.html</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>The Electric Pencil: Drawings from Inside State Hospital No. 3</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="C94" t="n">
+        <v>1</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-electric-pencil-drawings-from-inside-state-hospital-no-3_933/index.html</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>The Secret of Dreadwillow Carse</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>56.13</v>
+      </c>
+      <c r="C95" t="n">
+        <v>1</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-secret-of-dreadwillow-carse_944/index.html</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Masks and Shadows</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="C96" t="n">
+        <v>2</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/masks-and-shadows_909/index.html</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>The Pioneer Woman Cooks: Dinnertime: Comfort Classics, Freezer Food, 16-Minute Meals, and Other Delicious Ways to Solve Supper!</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>56.41</v>
+      </c>
+      <c r="C97" t="n">
+        <v>1</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-pioneer-woman-cooks-dinnertime-comfort-classics-freezer-food-16-minute-meals-and-other-delicious-ways-to-solve-supper_943/index.html</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>The Past Never Ends</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="C98" t="n">
+        <v>4</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-past-never-ends_942/index.html</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Our Band Could Be Your Life: Scenes from the American Indie Underground, 1981-1991</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="C99" t="n">
+        <v>3</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/our-band-could-be-your-life-scenes-from-the-american-indie-underground-1981-1991_985/index.html</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Slow States of Collapse: Poems</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="C100" t="n">
+        <v>3</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/slow-states-of-collapse-poems_960/index.html</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>The Death of Humanity: and the Case for Life</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="C101" t="n">
+        <v>4</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://books.toscrape.com/catalogue/the-death-of-humanity-and-the-case-for-life_932/index.html</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
